--- a/tests/acceptance/fixtures/xlsx/font.xlsx
+++ b/tests/acceptance/fixtures/xlsx/font.xlsx
@@ -10,6 +10,28 @@
   <definedNames/>
   <calcPr/>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -81,11 +103,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1" applyFill="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf xfId="0" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf xfId="0" borderId="0" fillId="0" fontId="1" numFmtId="0"/>
-    <xf xfId="0" borderId="0" fillId="0" fontId="2" numFmtId="0"/>
-    <xf xfId="0" borderId="0" fillId="0" fontId="3" numFmtId="0"/>
+    <xf xfId="0" borderId="0" fillId="0" fontId="0" numFmtId="0" quotePrefix="1"/>
+    <xf xfId="0" borderId="0" fillId="0" fontId="1" numFmtId="0" quotePrefix="1"/>
+    <xf xfId="0" borderId="0" fillId="0" fontId="2" numFmtId="0" quotePrefix="1"/>
+    <xf xfId="0" borderId="0" fillId="0" fontId="3" numFmtId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="normal" builtinId="0"/>
@@ -99,16 +122,16 @@
   <dimension ref="A1:D1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="1">
+      <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="3">
+      <c r="C1" t="s" s="4">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
     </row>

--- a/tests/acceptance/fixtures/xlsx/font.xlsx
+++ b/tests/acceptance/fixtures/xlsx/font.xlsx
@@ -56,7 +56,6 @@
   <fonts count="4">
     <font>
       <sz val="13"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
